--- a/Example/Extract Thermo-calc Results/output.xlsx
+++ b/Example/Extract Thermo-calc Results/output.xlsx
@@ -14,14 +14,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>w(Al)</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="127">
+  <si>
+    <t>File</t>
   </si>
   <si>
     <t>w(Mg)</t>
   </si>
   <si>
+    <t>w(Si)</t>
+  </si>
+  <si>
     <t>Liquidus_Temperature</t>
   </si>
   <si>
@@ -29,6 +32,369 @@
   </si>
   <si>
     <t>Melting_Range</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.00Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.01Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.02Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.03Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.04Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.05Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.06Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.07Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.08Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.09Mg0.10Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.00Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.01Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.02Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.03Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.04Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.05Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.06Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.07Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.08Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.09Si_np-T.exp</t>
+  </si>
+  <si>
+    <t>Al0.10Mg0.10Si_np-T.exp</t>
   </si>
 </sst>
 </file>
@@ -386,10 +752,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E122"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -405,2061 +771,2427 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>0</v>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
         <v>933.47083284</v>
       </c>
-      <c r="D2">
+      <c r="E2">
         <v>933.4708328</v>
       </c>
-      <c r="E2">
-        <v>3.999991804448655E-08</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
+      <c r="F2">
         <v>0</v>
       </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
       <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
         <v>0.01</v>
       </c>
-      <c r="C3">
+      <c r="D3">
         <v>927.64560363</v>
       </c>
-      <c r="D3">
+      <c r="E3">
         <v>883.50780418</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>44.13779944999999</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4">
         <v>0</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>0.02</v>
       </c>
-      <c r="C4">
+      <c r="D4">
         <v>921.71268794</v>
       </c>
-      <c r="D4">
+      <c r="E4">
         <v>850.74599744</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>70.96669050000003</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
         <v>0</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>0.03</v>
       </c>
-      <c r="C5">
+      <c r="D5">
         <v>915.66251971</v>
       </c>
-      <c r="D5">
+      <c r="E5">
         <v>850.74599743</v>
       </c>
-      <c r="E5">
+      <c r="F5">
         <v>64.91652227999998</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
         <v>0</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>0.04</v>
       </c>
-      <c r="C6">
+      <c r="D6">
         <v>909.48693397</v>
       </c>
-      <c r="D6">
+      <c r="E6">
         <v>850.74599743</v>
       </c>
-      <c r="E6">
+      <c r="F6">
         <v>58.74093654000001</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
         <v>0</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>0.05</v>
       </c>
-      <c r="C7">
+      <c r="D7">
         <v>903.17843366</v>
       </c>
-      <c r="D7">
+      <c r="E7">
         <v>850.74599743</v>
       </c>
-      <c r="E7">
+      <c r="F7">
         <v>52.43243623000001</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
         <v>0</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>0.06</v>
       </c>
-      <c r="C8">
+      <c r="D8">
         <v>896.73018078</v>
       </c>
-      <c r="D8">
+      <c r="E8">
         <v>850.74599742</v>
       </c>
-      <c r="E8">
+      <c r="F8">
         <v>45.98418335999997</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
         <v>0</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C9">
+      <c r="D9">
         <v>890.1359859</v>
       </c>
-      <c r="D9">
+      <c r="E9">
         <v>850.74599742</v>
       </c>
-      <c r="E9">
+      <c r="F9">
         <v>39.38998848000006</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
         <v>0</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>0.08</v>
       </c>
-      <c r="C10">
+      <c r="D10">
         <v>883.39029939</v>
       </c>
-      <c r="D10">
+      <c r="E10">
         <v>850.74599742</v>
       </c>
-      <c r="E10">
+      <c r="F10">
         <v>32.64430197000001</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
         <v>0</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>0.09</v>
       </c>
-      <c r="C11">
+      <c r="D11">
         <v>876.4882020700001</v>
       </c>
-      <c r="D11">
+      <c r="E11">
         <v>850.74599742</v>
       </c>
-      <c r="E11">
+      <c r="F11">
         <v>25.74220465000008</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+      <c r="B12">
         <v>0</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>0.1</v>
       </c>
-      <c r="C12">
+      <c r="D12">
         <v>869.42539646</v>
       </c>
-      <c r="D12">
+      <c r="E12">
         <v>850.74599742</v>
       </c>
-      <c r="E12">
+      <c r="F12">
         <v>18.67939904000002</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13">
         <v>0.01</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>0</v>
       </c>
-      <c r="C13">
+      <c r="D13">
         <v>928.40929505</v>
       </c>
-      <c r="D13">
+      <c r="E13">
         <v>917.66588314</v>
       </c>
-      <c r="E13">
+      <c r="F13">
         <v>10.74341190999996</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>0.01</v>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>18</v>
       </c>
       <c r="B14">
         <v>0.01</v>
       </c>
       <c r="C14">
+        <v>0.01</v>
+      </c>
+      <c r="D14">
         <v>922.7820010200001</v>
       </c>
-      <c r="D14">
+      <c r="E14">
         <v>849.25245423</v>
       </c>
-      <c r="E14">
+      <c r="F14">
         <v>73.52954679000004</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15">
         <v>0.01</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>0.02</v>
       </c>
-      <c r="C15">
+      <c r="D15">
         <v>917.04304059</v>
       </c>
-      <c r="D15">
-        <v>831.00944413</v>
-      </c>
       <c r="E15">
+        <v>831.00944413</v>
+      </c>
+      <c r="F15">
         <v>86.03359646000001</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16">
         <v>0.01</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>0.03</v>
       </c>
-      <c r="C16">
+      <c r="D16">
         <v>911.18390396</v>
       </c>
-      <c r="D16">
-        <v>831.00944413</v>
-      </c>
       <c r="E16">
+        <v>831.00944413</v>
+      </c>
+      <c r="F16">
         <v>80.17445982999993</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
+    <row r="17" spans="1:6">
+      <c r="A17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17">
         <v>0.01</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>0.04</v>
       </c>
-      <c r="C17">
+      <c r="D17">
         <v>905.19682341</v>
       </c>
-      <c r="D17">
-        <v>831.00944413</v>
-      </c>
       <c r="E17">
+        <v>831.00944413</v>
+      </c>
+      <c r="F17">
         <v>74.18737927999996</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
+    <row r="18" spans="1:6">
+      <c r="A18" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18">
         <v>0.01</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>0.05</v>
       </c>
-      <c r="C18">
+      <c r="D18">
         <v>899.07475666</v>
       </c>
-      <c r="D18">
-        <v>831.00944413</v>
-      </c>
       <c r="E18">
+        <v>831.00944413</v>
+      </c>
+      <c r="F18">
         <v>68.06531253000003</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
+    <row r="19" spans="1:6">
+      <c r="A19" t="s">
+        <v>23</v>
+      </c>
+      <c r="B19">
         <v>0.01</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>0.06</v>
       </c>
-      <c r="C19">
+      <c r="D19">
         <v>892.81137144</v>
       </c>
-      <c r="D19">
-        <v>831.00944413</v>
-      </c>
       <c r="E19">
+        <v>831.00944413</v>
+      </c>
+      <c r="F19">
         <v>61.80192731</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
+    <row r="20" spans="1:6">
+      <c r="A20" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20">
         <v>0.01</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C20">
+      <c r="D20">
         <v>886.40103085</v>
       </c>
-      <c r="D20">
-        <v>831.00944413</v>
-      </c>
       <c r="E20">
+        <v>831.00944413</v>
+      </c>
+      <c r="F20">
         <v>55.39158671999996</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
+    <row r="21" spans="1:6">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
         <v>0.01</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>0.08</v>
       </c>
-      <c r="C21">
+      <c r="D21">
         <v>879.8387788700001</v>
       </c>
-      <c r="D21">
-        <v>831.00944413</v>
-      </c>
       <c r="E21">
+        <v>831.00944413</v>
+      </c>
+      <c r="F21">
         <v>48.82933474000004</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
+    <row r="22" spans="1:6">
+      <c r="A22" t="s">
+        <v>26</v>
+      </c>
+      <c r="B22">
         <v>0.01</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>0.09</v>
       </c>
-      <c r="C22">
+      <c r="D22">
         <v>873.12032661</v>
       </c>
-      <c r="D22">
-        <v>831.00944413</v>
-      </c>
       <c r="E22">
+        <v>831.00944413</v>
+      </c>
+      <c r="F22">
         <v>42.11088247999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
+    <row r="23" spans="1:6">
+      <c r="A23" t="s">
+        <v>27</v>
+      </c>
+      <c r="B23">
         <v>0.01</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>0.1</v>
       </c>
-      <c r="C23">
+      <c r="D23">
         <v>866.2420389500001</v>
       </c>
-      <c r="D23">
-        <v>831.00944413</v>
-      </c>
       <c r="E23">
+        <v>831.00944413</v>
+      </c>
+      <c r="F23">
         <v>35.23259482000003</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
+    <row r="24" spans="1:6">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
         <v>0.02</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>0</v>
       </c>
-      <c r="C24">
+      <c r="D24">
         <v>923.35186615</v>
       </c>
-      <c r="D24">
+      <c r="E24">
         <v>901.5188316700001</v>
       </c>
-      <c r="E24">
+      <c r="F24">
         <v>21.83303447999992</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
+    <row r="25" spans="1:6">
+      <c r="A25" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25">
         <v>0.02</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>0.01</v>
       </c>
-      <c r="C25">
+      <c r="D25">
         <v>917.93230641</v>
       </c>
-      <c r="D25">
+      <c r="E25">
         <v>860.73832525</v>
       </c>
-      <c r="E25">
+      <c r="F25">
         <v>57.19398116000002</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>0.02</v>
+    <row r="26" spans="1:6">
+      <c r="A26" t="s">
+        <v>30</v>
       </c>
       <c r="B26">
         <v>0.02</v>
       </c>
       <c r="C26">
+        <v>0.02</v>
+      </c>
+      <c r="D26">
         <v>912.39770356</v>
       </c>
-      <c r="D26">
+      <c r="E26">
         <v>837.96611458</v>
       </c>
-      <c r="E26">
+      <c r="F26">
         <v>74.43158898000001</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
+    <row r="27" spans="1:6">
+      <c r="A27" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27">
         <v>0.02</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>0.03</v>
       </c>
-      <c r="C27">
+      <c r="D27">
         <v>906.73983245</v>
       </c>
-      <c r="D27">
-        <v>831.00944413</v>
-      </c>
       <c r="E27">
+        <v>831.00944413</v>
+      </c>
+      <c r="F27">
         <v>75.73038831999997</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
+    <row r="28" spans="1:6">
+      <c r="A28" t="s">
+        <v>32</v>
+      </c>
+      <c r="B28">
         <v>0.02</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>0.04</v>
       </c>
-      <c r="C28">
+      <c r="D28">
         <v>900.95127422</v>
       </c>
-      <c r="D28">
-        <v>831.00944413</v>
-      </c>
       <c r="E28">
+        <v>831.00944413</v>
+      </c>
+      <c r="F28">
         <v>69.94183008999994</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
+    <row r="29" spans="1:6">
+      <c r="A29" t="s">
+        <v>33</v>
+      </c>
+      <c r="B29">
         <v>0.02</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>0.05</v>
       </c>
-      <c r="C29">
+      <c r="D29">
         <v>895.0253933499999</v>
       </c>
-      <c r="D29">
-        <v>831.00944413</v>
-      </c>
       <c r="E29">
+        <v>831.00944413</v>
+      </c>
+      <c r="F29">
         <v>64.01594921999992</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
+    <row r="30" spans="1:6">
+      <c r="A30" t="s">
+        <v>34</v>
+      </c>
+      <c r="B30">
         <v>0.02</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>0.06</v>
       </c>
-      <c r="C30">
+      <c r="D30">
         <v>888.95631579</v>
       </c>
-      <c r="D30">
-        <v>831.00944413</v>
-      </c>
       <c r="E30">
+        <v>831.00944413</v>
+      </c>
+      <c r="F30">
         <v>57.94687165999994</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
+    <row r="31" spans="1:6">
+      <c r="A31" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31">
         <v>0.02</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C31">
+      <c r="D31">
         <v>882.73890825</v>
       </c>
-      <c r="D31">
-        <v>831.00944413</v>
-      </c>
       <c r="E31">
+        <v>831.00944413</v>
+      </c>
+      <c r="F31">
         <v>51.72946411999999</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
+    <row r="32" spans="1:6">
+      <c r="A32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B32">
         <v>0.02</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>0.08</v>
       </c>
-      <c r="C32">
+      <c r="D32">
         <v>876.36875847</v>
       </c>
-      <c r="D32">
-        <v>831.00944413</v>
-      </c>
       <c r="E32">
+        <v>831.00944413</v>
+      </c>
+      <c r="F32">
         <v>45.35931433999997</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
+    <row r="33" spans="1:6">
+      <c r="A33" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33">
         <v>0.02</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>0.09</v>
       </c>
-      <c r="C33">
+      <c r="D33">
         <v>869.8421561</v>
       </c>
-      <c r="D33">
-        <v>831.00944413</v>
-      </c>
       <c r="E33">
+        <v>831.00944413</v>
+      </c>
+      <c r="F33">
         <v>38.83271196999999</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
+    <row r="34" spans="1:6">
+      <c r="A34" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34">
         <v>0.02</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>0.1</v>
       </c>
-      <c r="C34">
+      <c r="D34">
         <v>863.15607455</v>
       </c>
-      <c r="D34">
-        <v>831.00944413</v>
-      </c>
       <c r="E34">
+        <v>831.00944413</v>
+      </c>
+      <c r="F34">
         <v>32.14663041999995</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
+    <row r="35" spans="1:6">
+      <c r="A35" t="s">
+        <v>39</v>
+      </c>
+      <c r="B35">
         <v>0.03</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>0</v>
       </c>
-      <c r="C35">
+      <c r="D35">
         <v>918.2873551500001</v>
       </c>
-      <c r="D35">
+      <c r="E35">
         <v>885.23330472</v>
       </c>
-      <c r="E35">
+      <c r="F35">
         <v>33.05405043000007</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
+    <row r="36" spans="1:6">
+      <c r="A36" t="s">
+        <v>40</v>
+      </c>
+      <c r="B36">
         <v>0.03</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>0.01</v>
       </c>
-      <c r="C36">
+      <c r="D36">
         <v>913.08507409</v>
       </c>
-      <c r="D36">
+      <c r="E36">
         <v>866.8694554</v>
       </c>
-      <c r="E36">
+      <c r="F36">
         <v>46.21561869000004</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
+    <row r="37" spans="1:6">
+      <c r="A37" t="s">
+        <v>41</v>
+      </c>
+      <c r="B37">
         <v>0.03</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>0.02</v>
       </c>
-      <c r="C37">
+      <c r="D37">
         <v>907.76423655</v>
       </c>
-      <c r="D37">
+      <c r="E37">
         <v>852.59330263</v>
       </c>
-      <c r="E37">
+      <c r="F37">
         <v>55.17093391999992</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>0.03</v>
+    <row r="38" spans="1:6">
+      <c r="A38" t="s">
+        <v>42</v>
       </c>
       <c r="B38">
         <v>0.03</v>
       </c>
       <c r="C38">
+        <v>0.03</v>
+      </c>
+      <c r="D38">
         <v>902.31685314</v>
       </c>
-      <c r="D38">
-        <v>831.00944413</v>
-      </c>
       <c r="E38">
+        <v>831.00944413</v>
+      </c>
+      <c r="F38">
         <v>71.30740901000001</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
-      <c r="A39">
+    <row r="39" spans="1:6">
+      <c r="A39" t="s">
+        <v>43</v>
+      </c>
+      <c r="B39">
         <v>0.03</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>0.04</v>
       </c>
-      <c r="C39">
+      <c r="D39">
         <v>896.7358081899999</v>
       </c>
-      <c r="D39">
-        <v>831.00944413</v>
-      </c>
       <c r="E39">
+        <v>831.00944413</v>
+      </c>
+      <c r="F39">
         <v>65.72636405999992</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
-      <c r="A40">
+    <row r="40" spans="1:6">
+      <c r="A40" t="s">
+        <v>44</v>
+      </c>
+      <c r="B40">
         <v>0.03</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>0.05</v>
       </c>
-      <c r="C40">
+      <c r="D40">
         <v>891.01482731</v>
       </c>
-      <c r="D40">
-        <v>831.00944413</v>
-      </c>
       <c r="E40">
+        <v>831.00944413</v>
+      </c>
+      <c r="F40">
         <v>60.00538317999997</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
-      <c r="A41">
+    <row r="41" spans="1:6">
+      <c r="A41" t="s">
+        <v>45</v>
+      </c>
+      <c r="B41">
         <v>0.03</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>0.06</v>
       </c>
-      <c r="C41">
+      <c r="D41">
         <v>885.14844945</v>
       </c>
-      <c r="D41">
-        <v>831.00944413</v>
-      </c>
       <c r="E41">
+        <v>831.00944413</v>
+      </c>
+      <c r="F41">
         <v>54.13900532000002</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
-      <c r="A42">
+    <row r="42" spans="1:6">
+      <c r="A42" t="s">
+        <v>46</v>
+      </c>
+      <c r="B42">
         <v>0.03</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C42">
+      <c r="D42">
         <v>879.13199945</v>
       </c>
-      <c r="D42">
-        <v>831.00944413</v>
-      </c>
       <c r="E42">
+        <v>831.00944413</v>
+      </c>
+      <c r="F42">
         <v>48.12255531999995</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
-      <c r="A43">
+    <row r="43" spans="1:6">
+      <c r="A43" t="s">
+        <v>47</v>
+      </c>
+      <c r="B43">
         <v>0.03</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>0.08</v>
       </c>
-      <c r="C43">
+      <c r="D43">
         <v>872.96156223</v>
       </c>
-      <c r="D43">
-        <v>831.00944413</v>
-      </c>
       <c r="E43">
+        <v>831.00944413</v>
+      </c>
+      <c r="F43">
         <v>41.95211810000001</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
-      <c r="A44">
+    <row r="44" spans="1:6">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44">
         <v>0.03</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>0.09</v>
       </c>
-      <c r="C44">
+      <c r="D44">
         <v>866.63395827</v>
       </c>
-      <c r="D44">
-        <v>831.00944413</v>
-      </c>
       <c r="E44">
+        <v>831.00944413</v>
+      </c>
+      <c r="F44">
         <v>35.62451413999997</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
-      <c r="A45">
+    <row r="45" spans="1:6">
+      <c r="A45" t="s">
+        <v>49</v>
+      </c>
+      <c r="B45">
         <v>0.03</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>0.1</v>
       </c>
-      <c r="C45">
+      <c r="D45">
         <v>860.14672014</v>
       </c>
-      <c r="D45">
-        <v>831.00944413</v>
-      </c>
       <c r="E45">
+        <v>831.00944413</v>
+      </c>
+      <c r="F45">
         <v>29.13727600999994</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
-      <c r="A46">
+    <row r="46" spans="1:6">
+      <c r="A46" t="s">
+        <v>50</v>
+      </c>
+      <c r="B46">
         <v>0.04</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>0</v>
       </c>
-      <c r="C46">
+      <c r="D46">
         <v>913.20565613</v>
       </c>
-      <c r="D46">
+      <c r="E46">
         <v>869.01704366</v>
       </c>
-      <c r="E46">
+      <c r="F46">
         <v>44.18861246999995</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
-      <c r="A47">
+    <row r="47" spans="1:6">
+      <c r="A47" t="s">
+        <v>51</v>
+      </c>
+      <c r="B47">
         <v>0.04</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>0.01</v>
       </c>
-      <c r="C47">
+      <c r="D47">
         <v>908.2292168</v>
       </c>
-      <c r="D47">
+      <c r="E47">
         <v>866.50970642</v>
       </c>
-      <c r="E47">
+      <c r="F47">
         <v>41.71951037999997</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
-      <c r="A48">
+    <row r="48" spans="1:6">
+      <c r="A48" t="s">
+        <v>52</v>
+      </c>
+      <c r="B48">
         <v>0.04</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>0.02</v>
       </c>
-      <c r="C48">
+      <c r="D48">
         <v>903.1305588</v>
       </c>
-      <c r="D48">
+      <c r="E48">
         <v>863.10754179</v>
       </c>
-      <c r="E48">
+      <c r="F48">
         <v>40.02301700999999</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
-      <c r="A49">
+    <row r="49" spans="1:6">
+      <c r="A49" t="s">
+        <v>53</v>
+      </c>
+      <c r="B49">
         <v>0.04</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>0.03</v>
       </c>
-      <c r="C49">
+      <c r="D49">
         <v>897.90188282</v>
       </c>
-      <c r="D49">
+      <c r="E49">
         <v>841.63879089</v>
       </c>
-      <c r="E49">
+      <c r="F49">
         <v>56.26309192999997</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
-      <c r="A50">
-        <v>0.04</v>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>54</v>
       </c>
       <c r="B50">
         <v>0.04</v>
       </c>
       <c r="C50">
+        <v>0.04</v>
+      </c>
+      <c r="D50">
         <v>892.53633094</v>
       </c>
-      <c r="D50">
-        <v>831.00944413</v>
-      </c>
       <c r="E50">
+        <v>831.00944413</v>
+      </c>
+      <c r="F50">
         <v>61.52688680999995</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
-      <c r="A51">
+    <row r="51" spans="1:6">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51">
         <v>0.04</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>0.05</v>
       </c>
-      <c r="C51">
+      <c r="D51">
         <v>887.0279474</v>
       </c>
-      <c r="D51">
-        <v>831.00944413</v>
-      </c>
       <c r="E51">
+        <v>831.00944413</v>
+      </c>
+      <c r="F51">
         <v>56.01850327</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
-      <c r="A52">
+    <row r="52" spans="1:6">
+      <c r="A52" t="s">
+        <v>56</v>
+      </c>
+      <c r="B52">
         <v>0.04</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>0.06</v>
       </c>
-      <c r="C52">
+      <c r="D52">
         <v>881.37164188</v>
       </c>
-      <c r="D52">
-        <v>831.00944413</v>
-      </c>
       <c r="E52">
+        <v>831.00944413</v>
+      </c>
+      <c r="F52">
         <v>50.36219774999995</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
-      <c r="A53">
+    <row r="53" spans="1:6">
+      <c r="A53" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53">
         <v>0.04</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C53">
+      <c r="D53">
         <v>875.56315507</v>
       </c>
-      <c r="D53">
-        <v>831.00944413</v>
-      </c>
       <c r="E53">
+        <v>831.00944413</v>
+      </c>
+      <c r="F53">
         <v>44.55371093999997</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
-      <c r="A54">
+    <row r="54" spans="1:6">
+      <c r="A54" t="s">
+        <v>58</v>
+      </c>
+      <c r="B54">
         <v>0.04</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>0.08</v>
       </c>
-      <c r="C54">
+      <c r="D54">
         <v>869.59902632</v>
       </c>
-      <c r="D54">
-        <v>831.00944413</v>
-      </c>
       <c r="E54">
+        <v>831.00944413</v>
+      </c>
+      <c r="F54">
         <v>38.58958218999999</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
-      <c r="A55">
+    <row r="55" spans="1:6">
+      <c r="A55" t="s">
+        <v>59</v>
+      </c>
+      <c r="B55">
         <v>0.04</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>0.09</v>
       </c>
-      <c r="C55">
+      <c r="D55">
         <v>863.47656309</v>
       </c>
-      <c r="D55">
-        <v>831.00944413</v>
-      </c>
       <c r="E55">
+        <v>831.00944413</v>
+      </c>
+      <c r="F55">
         <v>32.46711895999999</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
-      <c r="A56">
+    <row r="56" spans="1:6">
+      <c r="A56" t="s">
+        <v>60</v>
+      </c>
+      <c r="B56">
         <v>0.04</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>0.1</v>
       </c>
-      <c r="C56">
+      <c r="D56">
         <v>857.19381217</v>
       </c>
-      <c r="D56">
-        <v>831.00944413</v>
-      </c>
       <c r="E56">
+        <v>831.00944413</v>
+      </c>
+      <c r="F56">
         <v>26.18436803999998</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
-      <c r="A57">
+    <row r="57" spans="1:6">
+      <c r="A57" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57">
         <v>0.05</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>0</v>
       </c>
-      <c r="C57">
+      <c r="D57">
         <v>908.09706306</v>
       </c>
-      <c r="D57">
+      <c r="E57">
         <v>853.0561072</v>
       </c>
-      <c r="E57">
+      <c r="F57">
         <v>55.04095585999994</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
-      <c r="A58">
+    <row r="58" spans="1:6">
+      <c r="A58" t="s">
+        <v>62</v>
+      </c>
+      <c r="B58">
         <v>0.05</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>0.01</v>
       </c>
-      <c r="C58">
+      <c r="D58">
         <v>903.3540508999999</v>
       </c>
-      <c r="D58">
+      <c r="E58">
         <v>860.33275613</v>
       </c>
-      <c r="E58">
+      <c r="F58">
         <v>43.02129476999994</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
-      <c r="A59">
+    <row r="59" spans="1:6">
+      <c r="A59" t="s">
+        <v>63</v>
+      </c>
+      <c r="B59">
         <v>0.05</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>0.02</v>
       </c>
-      <c r="C59">
+      <c r="D59">
         <v>898.48500287</v>
       </c>
-      <c r="D59">
+      <c r="E59">
         <v>867.46121085</v>
       </c>
-      <c r="E59">
+      <c r="F59">
         <v>31.02379201999997</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
-      <c r="A60">
+    <row r="60" spans="1:6">
+      <c r="A60" t="s">
+        <v>64</v>
+      </c>
+      <c r="B60">
         <v>0.05</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>0.03</v>
       </c>
-      <c r="C60">
+      <c r="D60">
         <v>893.48226447</v>
       </c>
-      <c r="D60">
+      <c r="E60">
         <v>855.85552599</v>
       </c>
-      <c r="E60">
+      <c r="F60">
         <v>37.62673847999997</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
-      <c r="A61">
+    <row r="61" spans="1:6">
+      <c r="A61" t="s">
+        <v>65</v>
+      </c>
+      <c r="B61">
         <v>0.05</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>0.04</v>
       </c>
-      <c r="C61">
+      <c r="D61">
         <v>888.33919421</v>
       </c>
-      <c r="D61">
-        <v>831.00944413</v>
-      </c>
       <c r="E61">
+        <v>831.00944413</v>
+      </c>
+      <c r="F61">
         <v>57.32975007999994</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
-      <c r="A62">
-        <v>0.05</v>
+    <row r="62" spans="1:6">
+      <c r="A62" t="s">
+        <v>66</v>
       </c>
       <c r="B62">
         <v>0.05</v>
       </c>
       <c r="C62">
+        <v>0.05</v>
+      </c>
+      <c r="D62">
         <v>883.05011468</v>
       </c>
-      <c r="D62">
-        <v>831.00944413</v>
-      </c>
       <c r="E62">
+        <v>831.00944413</v>
+      </c>
+      <c r="F62">
         <v>52.04067054999996</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
-      <c r="A63">
+    <row r="63" spans="1:6">
+      <c r="A63" t="s">
+        <v>67</v>
+      </c>
+      <c r="B63">
         <v>0.05</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>0.06</v>
       </c>
-      <c r="C63">
+      <c r="D63">
         <v>877.61026708</v>
       </c>
-      <c r="D63">
-        <v>831.00944413</v>
-      </c>
       <c r="E63">
+        <v>831.00944413</v>
+      </c>
+      <c r="F63">
         <v>46.60082294999995</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
-      <c r="A64">
+    <row r="64" spans="1:6">
+      <c r="A64" t="s">
+        <v>68</v>
+      </c>
+      <c r="B64">
         <v>0.05</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C64">
+      <c r="D64">
         <v>872.01576899</v>
       </c>
-      <c r="D64">
-        <v>831.00944413</v>
-      </c>
       <c r="E64">
+        <v>831.00944413</v>
+      </c>
+      <c r="F64">
         <v>41.00632485999995</v>
       </c>
     </row>
-    <row r="65" spans="1:5">
-      <c r="A65">
+    <row r="65" spans="1:6">
+      <c r="A65" t="s">
+        <v>69</v>
+      </c>
+      <c r="B65">
         <v>0.05</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>0.08</v>
       </c>
-      <c r="C65">
+      <c r="D65">
         <v>866.26357501</v>
       </c>
-      <c r="D65">
+      <c r="E65">
         <v>831.00944419</v>
       </c>
-      <c r="E65">
+      <c r="F65">
         <v>35.25413082</v>
       </c>
     </row>
-    <row r="66" spans="1:5">
-      <c r="A66">
+    <row r="66" spans="1:6">
+      <c r="A66" t="s">
+        <v>70</v>
+      </c>
+      <c r="B66">
         <v>0.05</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>0.09</v>
       </c>
-      <c r="C66">
+      <c r="D66">
         <v>860.35143983</v>
       </c>
-      <c r="D66">
-        <v>831.00944413</v>
-      </c>
       <c r="E66">
+        <v>831.00944413</v>
+      </c>
+      <c r="F66">
         <v>29.34199569999998</v>
       </c>
     </row>
-    <row r="67" spans="1:5">
-      <c r="A67">
+    <row r="67" spans="1:6">
+      <c r="A67" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67">
         <v>0.05</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>0.1</v>
       </c>
-      <c r="C67">
+      <c r="D67">
         <v>854.2778836799999</v>
       </c>
-      <c r="D67">
-        <v>831.00944413</v>
-      </c>
       <c r="E67">
+        <v>831.00944413</v>
+      </c>
+      <c r="F67">
         <v>23.26843954999993</v>
       </c>
     </row>
-    <row r="68" spans="1:5">
-      <c r="A68">
+    <row r="68" spans="1:6">
+      <c r="A68" t="s">
+        <v>72</v>
+      </c>
+      <c r="B68">
         <v>0.06</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>0</v>
       </c>
-      <c r="C68">
+      <c r="D68">
         <v>902.95230502</v>
       </c>
-      <c r="D68">
+      <c r="E68">
         <v>837.50165821</v>
       </c>
-      <c r="E68">
+      <c r="F68">
         <v>65.45064681000008</v>
       </c>
     </row>
-    <row r="69" spans="1:5">
-      <c r="A69">
+    <row r="69" spans="1:6">
+      <c r="A69" t="s">
+        <v>73</v>
+      </c>
+      <c r="B69">
         <v>0.06</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>0.01</v>
       </c>
-      <c r="C69">
+      <c r="D69">
         <v>898.4493349099999</v>
       </c>
-      <c r="D69">
+      <c r="E69">
         <v>850.20142242</v>
       </c>
-      <c r="E69">
+      <c r="F69">
         <v>48.24791248999998</v>
       </c>
     </row>
-    <row r="70" spans="1:5">
-      <c r="A70">
+    <row r="70" spans="1:6">
+      <c r="A70" t="s">
+        <v>74</v>
+      </c>
+      <c r="B70">
         <v>0.06</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>0.02</v>
       </c>
-      <c r="C70">
+      <c r="D70">
         <v>893.81635509</v>
       </c>
-      <c r="D70">
+      <c r="E70">
         <v>864.96542916</v>
       </c>
-      <c r="E70">
+      <c r="F70">
         <v>28.85092593000002</v>
       </c>
     </row>
-    <row r="71" spans="1:5">
-      <c r="A71">
+    <row r="71" spans="1:6">
+      <c r="A71" t="s">
+        <v>75</v>
+      </c>
+      <c r="B71">
         <v>0.06</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>0.03</v>
       </c>
-      <c r="C71">
+      <c r="D71">
         <v>889.04581416</v>
       </c>
-      <c r="D71">
+      <c r="E71">
         <v>865.09262552</v>
       </c>
-      <c r="E71">
+      <c r="F71">
         <v>23.95318864000001</v>
       </c>
     </row>
-    <row r="72" spans="1:5">
-      <c r="A72">
+    <row r="72" spans="1:6">
+      <c r="A72" t="s">
+        <v>76</v>
+      </c>
+      <c r="B72">
         <v>0.06</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>0.04</v>
       </c>
-      <c r="C72">
+      <c r="D72">
         <v>884.13124581</v>
       </c>
-      <c r="D72">
+      <c r="E72">
         <v>845.38861592</v>
       </c>
-      <c r="E72">
+      <c r="F72">
         <v>38.74262988999999</v>
       </c>
     </row>
-    <row r="73" spans="1:5">
-      <c r="A73">
+    <row r="73" spans="1:6">
+      <c r="A73" t="s">
+        <v>77</v>
+      </c>
+      <c r="B73">
         <v>0.06</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>0.05</v>
       </c>
-      <c r="C73">
+      <c r="D73">
         <v>879.0672154600001</v>
       </c>
-      <c r="D73">
-        <v>831.00944413</v>
-      </c>
       <c r="E73">
+        <v>831.00944413</v>
+      </c>
+      <c r="F73">
         <v>48.05777133000004</v>
       </c>
     </row>
-    <row r="74" spans="1:5">
-      <c r="A74">
-        <v>0.06</v>
+    <row r="74" spans="1:6">
+      <c r="A74" t="s">
+        <v>78</v>
       </c>
       <c r="B74">
         <v>0.06</v>
       </c>
       <c r="C74">
+        <v>0.06</v>
+      </c>
+      <c r="D74">
         <v>873.849259</v>
       </c>
-      <c r="D74">
+      <c r="E74">
         <v>831.00944419</v>
       </c>
-      <c r="E74">
+      <c r="F74">
         <v>42.83981481000001</v>
       </c>
     </row>
-    <row r="75" spans="1:5">
-      <c r="A75">
+    <row r="75" spans="1:6">
+      <c r="A75" t="s">
+        <v>79</v>
+      </c>
+      <c r="B75">
         <v>0.06</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C75">
+      <c r="D75">
         <v>868.47383528</v>
       </c>
-      <c r="D75">
-        <v>831.00944413</v>
-      </c>
       <c r="E75">
+        <v>831.00944413</v>
+      </c>
+      <c r="F75">
         <v>37.46439114999998</v>
       </c>
     </row>
-    <row r="76" spans="1:5">
-      <c r="A76">
+    <row r="76" spans="1:6">
+      <c r="A76" t="s">
+        <v>80</v>
+      </c>
+      <c r="B76">
         <v>0.06</v>
       </c>
-      <c r="B76">
+      <c r="C76">
         <v>0.08</v>
       </c>
-      <c r="C76">
+      <c r="D76">
         <v>862.9382785</v>
       </c>
-      <c r="D76">
-        <v>831.00944413</v>
-      </c>
       <c r="E76">
+        <v>831.00944413</v>
+      </c>
+      <c r="F76">
         <v>31.92883437</v>
       </c>
     </row>
-    <row r="77" spans="1:5">
-      <c r="A77">
+    <row r="77" spans="1:6">
+      <c r="A77" t="s">
+        <v>81</v>
+      </c>
+      <c r="B77">
         <v>0.06</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>0.09</v>
       </c>
-      <c r="C77">
+      <c r="D77">
         <v>857.2407545</v>
       </c>
-      <c r="D77">
-        <v>831.00944413</v>
-      </c>
       <c r="E77">
+        <v>831.00944413</v>
+      </c>
+      <c r="F77">
         <v>26.23131036999996</v>
       </c>
     </row>
-    <row r="78" spans="1:5">
-      <c r="A78">
+    <row r="78" spans="1:6">
+      <c r="A78" t="s">
+        <v>82</v>
+      </c>
+      <c r="B78">
         <v>0.06</v>
       </c>
-      <c r="B78">
+      <c r="C78">
         <v>0.1</v>
       </c>
-      <c r="C78">
+      <c r="D78">
         <v>851.38022031</v>
       </c>
-      <c r="D78">
+      <c r="E78">
         <v>831.00944419</v>
       </c>
-      <c r="E78">
+      <c r="F78">
         <v>20.37077612000007</v>
       </c>
     </row>
-    <row r="79" spans="1:5">
-      <c r="A79">
+    <row r="79" spans="1:6">
+      <c r="A79" t="s">
+        <v>83</v>
+      </c>
+      <c r="B79">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B79">
+      <c r="C79">
         <v>0</v>
       </c>
-      <c r="C79">
+      <c r="D79">
         <v>897.76257263</v>
       </c>
-      <c r="D79">
+      <c r="E79">
         <v>822.4670124</v>
       </c>
-      <c r="E79">
+      <c r="F79">
         <v>75.29556022999998</v>
       </c>
     </row>
-    <row r="80" spans="1:5">
-      <c r="A80">
+    <row r="80" spans="1:6">
+      <c r="A80" t="s">
+        <v>84</v>
+      </c>
+      <c r="B80">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B80">
+      <c r="C80">
         <v>0.01</v>
       </c>
-      <c r="C80">
+      <c r="D80">
         <v>893.50529937</v>
       </c>
-      <c r="D80">
+      <c r="E80">
         <v>837.89486575</v>
       </c>
-      <c r="E80">
+      <c r="F80">
         <v>55.61043361999998</v>
       </c>
     </row>
-    <row r="81" spans="1:5">
-      <c r="A81">
+    <row r="81" spans="1:6">
+      <c r="A81" t="s">
+        <v>85</v>
+      </c>
+      <c r="B81">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B81">
+      <c r="C81">
         <v>0.02</v>
       </c>
-      <c r="C81">
+      <c r="D81">
         <v>889.11388987</v>
       </c>
-      <c r="D81">
+      <c r="E81">
         <v>856.92492458</v>
       </c>
-      <c r="E81">
+      <c r="F81">
         <v>32.18896528999994</v>
       </c>
     </row>
-    <row r="82" spans="1:5">
-      <c r="A82">
+    <row r="82" spans="1:6">
+      <c r="A82" t="s">
+        <v>86</v>
+      </c>
+      <c r="B82">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B82">
+      <c r="C82">
         <v>0.03</v>
       </c>
-      <c r="C82">
+      <c r="D82">
         <v>884.58085428</v>
       </c>
-      <c r="D82">
+      <c r="E82">
         <v>867.37597327</v>
       </c>
-      <c r="E82">
+      <c r="F82">
         <v>17.20488101000001</v>
       </c>
     </row>
-    <row r="83" spans="1:5">
-      <c r="A83">
+    <row r="83" spans="1:6">
+      <c r="A83" t="s">
+        <v>87</v>
+      </c>
+      <c r="B83">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B83">
+      <c r="C83">
         <v>0.04</v>
       </c>
-      <c r="C83">
+      <c r="D83">
         <v>879.8998688</v>
       </c>
-      <c r="D83">
+      <c r="E83">
         <v>858.9591517600001</v>
       </c>
-      <c r="E83">
+      <c r="F83">
         <v>20.94071703999998</v>
       </c>
     </row>
-    <row r="84" spans="1:5">
-      <c r="A84">
+    <row r="84" spans="1:6">
+      <c r="A84" t="s">
+        <v>88</v>
+      </c>
+      <c r="B84">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B84">
+      <c r="C84">
         <v>0.05</v>
       </c>
-      <c r="C84">
+      <c r="D84">
         <v>875.06570182</v>
       </c>
-      <c r="D84">
+      <c r="E84">
         <v>832.27931836</v>
       </c>
-      <c r="E84">
+      <c r="F84">
         <v>42.78638345999991</v>
       </c>
     </row>
-    <row r="85" spans="1:5">
-      <c r="A85">
+    <row r="85" spans="1:6">
+      <c r="A85" t="s">
+        <v>89</v>
+      </c>
+      <c r="B85">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B85">
+      <c r="C85">
         <v>0.06</v>
       </c>
-      <c r="C85">
+      <c r="D85">
         <v>870.0741541800001</v>
       </c>
-      <c r="D85">
-        <v>831.00944413</v>
-      </c>
       <c r="E85">
+        <v>831.00944413</v>
+      </c>
+      <c r="F85">
         <v>39.06471005000003</v>
       </c>
     </row>
-    <row r="86" spans="1:5">
-      <c r="A86">
-        <v>0.07000000000000001</v>
+    <row r="86" spans="1:6">
+      <c r="A86" t="s">
+        <v>90</v>
       </c>
       <c r="B86">
         <v>0.07000000000000001</v>
       </c>
       <c r="C86">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D86">
         <v>864.92199037</v>
       </c>
-      <c r="D86">
-        <v>831.00944413</v>
-      </c>
       <c r="E86">
+        <v>831.00944413</v>
+      </c>
+      <c r="F86">
         <v>33.91254623999998</v>
       </c>
     </row>
-    <row r="87" spans="1:5">
-      <c r="A87">
+    <row r="87" spans="1:6">
+      <c r="A87" t="s">
+        <v>91</v>
+      </c>
+      <c r="B87">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B87">
+      <c r="C87">
         <v>0.08</v>
       </c>
-      <c r="C87">
+      <c r="D87">
         <v>860.70985063</v>
       </c>
-      <c r="D87">
-        <v>831.00944413</v>
-      </c>
       <c r="E87">
+        <v>831.00944413</v>
+      </c>
+      <c r="F87">
         <v>29.70040649999999</v>
       </c>
     </row>
-    <row r="88" spans="1:5">
-      <c r="A88">
+    <row r="88" spans="1:6">
+      <c r="A88" t="s">
+        <v>92</v>
+      </c>
+      <c r="B88">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B88">
+      <c r="C88">
         <v>0.09</v>
       </c>
-      <c r="C88">
+      <c r="D88">
         <v>863.96292004</v>
       </c>
-      <c r="D88">
-        <v>831.00944413</v>
-      </c>
       <c r="E88">
+        <v>831.00944413</v>
+      </c>
+      <c r="F88">
         <v>32.95347590999995</v>
       </c>
     </row>
-    <row r="89" spans="1:5">
-      <c r="A89">
+    <row r="89" spans="1:6">
+      <c r="A89" t="s">
+        <v>93</v>
+      </c>
+      <c r="B89">
         <v>0.07000000000000001</v>
       </c>
-      <c r="B89">
+      <c r="C89">
         <v>0.1</v>
       </c>
-      <c r="C89">
+      <c r="D89">
         <v>866.5063467799999</v>
       </c>
-      <c r="D89">
-        <v>831.00944413</v>
-      </c>
       <c r="E89">
+        <v>831.00944413</v>
+      </c>
+      <c r="F89">
         <v>35.49690264999992</v>
       </c>
     </row>
-    <row r="90" spans="1:5">
-      <c r="A90">
+    <row r="90" spans="1:6">
+      <c r="A90" t="s">
+        <v>94</v>
+      </c>
+      <c r="B90">
         <v>0.08</v>
       </c>
-      <c r="B90">
+      <c r="C90">
         <v>0</v>
       </c>
-      <c r="C90">
+      <c r="D90">
         <v>892.5195383499999</v>
       </c>
-      <c r="D90">
+      <c r="E90">
         <v>808.0305919800001</v>
       </c>
-      <c r="E90">
+      <c r="F90">
         <v>84.48894636999989</v>
       </c>
     </row>
-    <row r="91" spans="1:5">
-      <c r="A91">
+    <row r="91" spans="1:6">
+      <c r="A91" t="s">
+        <v>95</v>
+      </c>
+      <c r="B91">
         <v>0.08</v>
       </c>
-      <c r="B91">
+      <c r="C91">
         <v>0.01</v>
       </c>
-      <c r="C91">
+      <c r="D91">
         <v>888.51267006</v>
       </c>
-      <c r="D91">
+      <c r="E91">
         <v>824.6120174</v>
       </c>
-      <c r="E91">
+      <c r="F91">
         <v>63.90065265999999</v>
       </c>
     </row>
-    <row r="92" spans="1:5">
-      <c r="A92">
+    <row r="92" spans="1:6">
+      <c r="A92" t="s">
+        <v>96</v>
+      </c>
+      <c r="B92">
         <v>0.08</v>
       </c>
-      <c r="B92">
+      <c r="C92">
         <v>0.02</v>
       </c>
-      <c r="C92">
+      <c r="D92">
         <v>884.3673949499999</v>
       </c>
-      <c r="D92">
+      <c r="E92">
         <v>845.4553015400001</v>
       </c>
-      <c r="E92">
+      <c r="F92">
         <v>38.9120934099999</v>
       </c>
     </row>
-    <row r="93" spans="1:5">
-      <c r="A93">
+    <row r="93" spans="1:6">
+      <c r="A93" t="s">
+        <v>97</v>
+      </c>
+      <c r="B93">
         <v>0.08</v>
       </c>
-      <c r="B93">
+      <c r="C93">
         <v>0.03</v>
       </c>
-      <c r="C93">
+      <c r="D93">
         <v>880.07624681</v>
       </c>
-      <c r="D93">
+      <c r="E93">
         <v>862.65357887</v>
       </c>
-      <c r="E93">
+      <c r="F93">
         <v>17.42266794</v>
       </c>
     </row>
-    <row r="94" spans="1:5">
-      <c r="A94">
+    <row r="94" spans="1:6">
+      <c r="A94" t="s">
+        <v>98</v>
+      </c>
+      <c r="B94">
         <v>0.08</v>
       </c>
-      <c r="B94">
+      <c r="C94">
         <v>0.04</v>
       </c>
-      <c r="C94">
+      <c r="D94">
         <v>875.6330083</v>
       </c>
-      <c r="D94">
+      <c r="E94">
         <v>866.56699295</v>
       </c>
-      <c r="E94">
+      <c r="F94">
         <v>9.066015350000043</v>
       </c>
     </row>
-    <row r="95" spans="1:5">
-      <c r="A95">
+    <row r="95" spans="1:6">
+      <c r="A95" t="s">
+        <v>99</v>
+      </c>
+      <c r="B95">
         <v>0.08</v>
       </c>
-      <c r="B95">
+      <c r="C95">
         <v>0.05</v>
       </c>
-      <c r="C95">
+      <c r="D95">
         <v>871.03262134</v>
       </c>
-      <c r="D95">
+      <c r="E95">
         <v>849.17506502</v>
       </c>
-      <c r="E95">
+      <c r="F95">
         <v>21.85755631999996</v>
       </c>
     </row>
-    <row r="96" spans="1:5">
-      <c r="A96">
+    <row r="96" spans="1:6">
+      <c r="A96" t="s">
+        <v>100</v>
+      </c>
+      <c r="B96">
         <v>0.08</v>
       </c>
-      <c r="B96">
+      <c r="C96">
         <v>0.06</v>
       </c>
-      <c r="C96">
+      <c r="D96">
         <v>866.27111728</v>
       </c>
-      <c r="D96">
-        <v>831.00944413</v>
-      </c>
       <c r="E96">
+        <v>831.00944413</v>
+      </c>
+      <c r="F96">
         <v>35.26167314999998</v>
       </c>
     </row>
-    <row r="97" spans="1:5">
-      <c r="A97">
+    <row r="97" spans="1:6">
+      <c r="A97" t="s">
+        <v>101</v>
+      </c>
+      <c r="B97">
         <v>0.08</v>
       </c>
-      <c r="B97">
+      <c r="C97">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C97">
+      <c r="D97">
         <v>869.9946177</v>
       </c>
-      <c r="D97">
-        <v>831.00944413</v>
-      </c>
       <c r="E97">
+        <v>831.00944413</v>
+      </c>
+      <c r="F97">
         <v>38.98517357000003</v>
       </c>
     </row>
-    <row r="98" spans="1:5">
-      <c r="A98">
-        <v>0.08</v>
+    <row r="98" spans="1:6">
+      <c r="A98" t="s">
+        <v>102</v>
       </c>
       <c r="B98">
         <v>0.08</v>
       </c>
       <c r="C98">
+        <v>0.08</v>
+      </c>
+      <c r="D98">
         <v>874.50205003</v>
       </c>
-      <c r="D98">
-        <v>831.00944413</v>
-      </c>
       <c r="E98">
+        <v>831.00944413</v>
+      </c>
+      <c r="F98">
         <v>43.49260589999994</v>
       </c>
     </row>
-    <row r="99" spans="1:5">
-      <c r="A99">
+    <row r="99" spans="1:6">
+      <c r="A99" t="s">
+        <v>103</v>
+      </c>
+      <c r="B99">
         <v>0.08</v>
       </c>
-      <c r="B99">
+      <c r="C99">
         <v>0.09</v>
       </c>
-      <c r="C99">
+      <c r="D99">
         <v>878.10070754</v>
       </c>
-      <c r="D99">
-        <v>831.00944413</v>
-      </c>
       <c r="E99">
+        <v>831.00944413</v>
+      </c>
+      <c r="F99">
         <v>47.09126341000001</v>
       </c>
     </row>
-    <row r="100" spans="1:5">
-      <c r="A100">
+    <row r="100" spans="1:6">
+      <c r="A100" t="s">
+        <v>104</v>
+      </c>
+      <c r="B100">
         <v>0.08</v>
       </c>
-      <c r="B100">
+      <c r="C100">
         <v>0.1</v>
       </c>
-      <c r="C100">
+      <c r="D100">
         <v>880.96666056</v>
       </c>
-      <c r="D100">
-        <v>831.00944413</v>
-      </c>
       <c r="E100">
+        <v>831.00944413</v>
+      </c>
+      <c r="F100">
         <v>49.95721643000002</v>
       </c>
     </row>
-    <row r="101" spans="1:5">
-      <c r="A101">
+    <row r="101" spans="1:6">
+      <c r="A101" t="s">
+        <v>105</v>
+      </c>
+      <c r="B101">
         <v>0.09</v>
       </c>
-      <c r="B101">
+      <c r="C101">
         <v>0</v>
       </c>
-      <c r="C101">
+      <c r="D101">
         <v>887.2153719299999</v>
       </c>
-      <c r="D101">
+      <c r="E101">
         <v>794.24124527</v>
       </c>
-      <c r="E101">
+      <c r="F101">
         <v>92.97412665999991</v>
       </c>
     </row>
-    <row r="102" spans="1:5">
-      <c r="A102">
+    <row r="102" spans="1:6">
+      <c r="A102" t="s">
+        <v>106</v>
+      </c>
+      <c r="B102">
         <v>0.09</v>
       </c>
-      <c r="B102">
+      <c r="C102">
         <v>0.01</v>
       </c>
-      <c r="C102">
+      <c r="D102">
         <v>883.46268522</v>
       </c>
-      <c r="D102">
+      <c r="E102">
         <v>811.06285024</v>
       </c>
-      <c r="E102">
+      <c r="F102">
         <v>72.39983498000004</v>
       </c>
     </row>
-    <row r="103" spans="1:5">
-      <c r="A103">
+    <row r="103" spans="1:6">
+      <c r="A103" t="s">
+        <v>107</v>
+      </c>
+      <c r="B103">
         <v>0.09</v>
       </c>
-      <c r="B103">
+      <c r="C103">
         <v>0.02</v>
       </c>
-      <c r="C103">
+      <c r="D103">
         <v>879.5671900900001</v>
       </c>
-      <c r="D103">
+      <c r="E103">
         <v>832.26274698</v>
       </c>
-      <c r="E103">
+      <c r="F103">
         <v>47.30444311000008</v>
       </c>
     </row>
-    <row r="104" spans="1:5">
-      <c r="A104">
+    <row r="104" spans="1:6">
+      <c r="A104" t="s">
+        <v>108</v>
+      </c>
+      <c r="B104">
         <v>0.09</v>
       </c>
-      <c r="B104">
+      <c r="C104">
         <v>0.03</v>
       </c>
-      <c r="C104">
+      <c r="D104">
         <v>875.52140881</v>
       </c>
-      <c r="D104">
+      <c r="E104">
         <v>852.83469927</v>
       </c>
-      <c r="E104">
+      <c r="F104">
         <v>22.68670954000004</v>
       </c>
     </row>
-    <row r="105" spans="1:5">
-      <c r="A105">
+    <row r="105" spans="1:6">
+      <c r="A105" t="s">
+        <v>109</v>
+      </c>
+      <c r="B105">
         <v>0.09</v>
       </c>
-      <c r="B105">
+      <c r="C105">
         <v>0.04</v>
       </c>
-      <c r="C105">
+      <c r="D105">
         <v>871.31919486</v>
       </c>
-      <c r="D105">
+      <c r="E105">
         <v>866.51411196</v>
       </c>
-      <c r="E105">
+      <c r="F105">
         <v>4.805082900000002</v>
       </c>
     </row>
-    <row r="106" spans="1:5">
-      <c r="A106">
+    <row r="106" spans="1:6">
+      <c r="A106" t="s">
+        <v>110</v>
+      </c>
+      <c r="B106">
         <v>0.09</v>
       </c>
-      <c r="B106">
+      <c r="C106">
         <v>0.05</v>
       </c>
-      <c r="C106">
+      <c r="D106">
         <v>868.2252457</v>
       </c>
-      <c r="D106">
+      <c r="E106">
         <v>861.7992586</v>
       </c>
-      <c r="E106">
+      <c r="F106">
         <v>6.425987099999929</v>
       </c>
     </row>
-    <row r="107" spans="1:5">
-      <c r="A107">
+    <row r="107" spans="1:6">
+      <c r="A107" t="s">
+        <v>111</v>
+      </c>
+      <c r="B107">
         <v>0.09</v>
       </c>
-      <c r="B107">
+      <c r="C107">
         <v>0.06</v>
       </c>
-      <c r="C107">
+      <c r="D107">
         <v>875.89452044</v>
       </c>
-      <c r="D107">
+      <c r="E107">
         <v>836.29690139</v>
       </c>
-      <c r="E107">
+      <c r="F107">
         <v>39.59761904999993</v>
       </c>
     </row>
-    <row r="108" spans="1:5">
-      <c r="A108">
+    <row r="108" spans="1:6">
+      <c r="A108" t="s">
+        <v>112</v>
+      </c>
+      <c r="B108">
         <v>0.09</v>
       </c>
-      <c r="B108">
+      <c r="C108">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C108">
+      <c r="D108">
         <v>881.95928606</v>
       </c>
-      <c r="D108">
-        <v>831.00944413</v>
-      </c>
       <c r="E108">
+        <v>831.00944413</v>
+      </c>
+      <c r="F108">
         <v>50.94984192999993</v>
       </c>
     </row>
-    <row r="109" spans="1:5">
-      <c r="A109">
+    <row r="109" spans="1:6">
+      <c r="A109" t="s">
+        <v>113</v>
+      </c>
+      <c r="B109">
         <v>0.09</v>
       </c>
-      <c r="B109">
+      <c r="C109">
         <v>0.08</v>
       </c>
-      <c r="C109">
+      <c r="D109">
         <v>886.82475777</v>
       </c>
-      <c r="D109">
-        <v>831.00944413</v>
-      </c>
       <c r="E109">
+        <v>831.00944413</v>
+      </c>
+      <c r="F109">
         <v>55.81531364</v>
       </c>
     </row>
-    <row r="110" spans="1:5">
-      <c r="A110">
-        <v>0.09</v>
+    <row r="110" spans="1:6">
+      <c r="A110" t="s">
+        <v>114</v>
       </c>
       <c r="B110">
         <v>0.09</v>
       </c>
       <c r="C110">
+        <v>0.09</v>
+      </c>
+      <c r="D110">
         <v>890.7549747100001</v>
       </c>
-      <c r="D110">
-        <v>831.00944413</v>
-      </c>
       <c r="E110">
+        <v>831.00944413</v>
+      </c>
+      <c r="F110">
         <v>59.74553058000004</v>
       </c>
     </row>
-    <row r="111" spans="1:5">
-      <c r="A111">
+    <row r="111" spans="1:6">
+      <c r="A111" t="s">
+        <v>115</v>
+      </c>
+      <c r="B111">
         <v>0.09</v>
       </c>
-      <c r="B111">
+      <c r="C111">
         <v>0.1</v>
       </c>
-      <c r="C111">
+      <c r="D111">
         <v>893.93104177</v>
       </c>
-      <c r="D111">
-        <v>831.00944413</v>
-      </c>
       <c r="E111">
+        <v>831.00944413</v>
+      </c>
+      <c r="F111">
         <v>62.92159763999996</v>
       </c>
     </row>
-    <row r="112" spans="1:5">
-      <c r="A112">
+    <row r="112" spans="1:6">
+      <c r="A112" t="s">
+        <v>116</v>
+      </c>
+      <c r="B112">
         <v>0.1</v>
       </c>
-      <c r="B112">
+      <c r="C112">
         <v>0</v>
       </c>
-      <c r="C112">
+      <c r="D112">
         <v>881.84275102</v>
       </c>
-      <c r="D112">
+      <c r="E112">
         <v>781.1239596299999</v>
       </c>
-      <c r="E112">
+      <c r="F112">
         <v>100.7187913900001</v>
       </c>
     </row>
-    <row r="113" spans="1:5">
-      <c r="A113">
+    <row r="113" spans="1:6">
+      <c r="A113" t="s">
+        <v>117</v>
+      </c>
+      <c r="B113">
         <v>0.1</v>
       </c>
-      <c r="B113">
+      <c r="C113">
         <v>0.01</v>
       </c>
-      <c r="C113">
+      <c r="D113">
         <v>878.34710774</v>
       </c>
-      <c r="D113">
+      <c r="E113">
         <v>797.6536992600001</v>
       </c>
-      <c r="E113">
+      <c r="F113">
         <v>80.6934084799999</v>
       </c>
     </row>
-    <row r="114" spans="1:5">
-      <c r="A114">
+    <row r="114" spans="1:6">
+      <c r="A114" t="s">
+        <v>118</v>
+      </c>
+      <c r="B114">
         <v>0.1</v>
       </c>
-      <c r="B114">
+      <c r="C114">
         <v>0.02</v>
       </c>
-      <c r="C114">
+      <c r="D114">
         <v>874.7041397</v>
       </c>
-      <c r="D114">
+      <c r="E114">
         <v>818.40828773</v>
       </c>
-      <c r="E114">
+      <c r="F114">
         <v>56.29585197000006</v>
       </c>
     </row>
-    <row r="115" spans="1:5">
-      <c r="A115">
+    <row r="115" spans="1:6">
+      <c r="A115" t="s">
+        <v>119</v>
+      </c>
+      <c r="B115">
         <v>0.1</v>
       </c>
-      <c r="B115">
+      <c r="C115">
         <v>0.03</v>
       </c>
-      <c r="C115">
+      <c r="D115">
         <v>870.90632341</v>
       </c>
-      <c r="D115">
+      <c r="E115">
         <v>840.15191385</v>
       </c>
-      <c r="E115">
+      <c r="F115">
         <v>30.75440956</v>
       </c>
     </row>
-    <row r="116" spans="1:5">
-      <c r="A116">
+    <row r="116" spans="1:6">
+      <c r="A116" t="s">
+        <v>120</v>
+      </c>
+      <c r="B116">
         <v>0.1</v>
       </c>
-      <c r="B116">
+      <c r="C116">
         <v>0.04</v>
       </c>
-      <c r="C116">
+      <c r="D116">
         <v>867.81147309</v>
       </c>
-      <c r="D116">
+      <c r="E116">
         <v>859.54659171</v>
       </c>
-      <c r="E116">
+      <c r="F116">
         <v>8.26488138000002</v>
       </c>
     </row>
-    <row r="117" spans="1:5">
-      <c r="A117">
+    <row r="117" spans="1:6">
+      <c r="A117" t="s">
+        <v>121</v>
+      </c>
+      <c r="B117">
         <v>0.1</v>
       </c>
-      <c r="B117">
+      <c r="C117">
         <v>0.05</v>
       </c>
-      <c r="C117">
+      <c r="D117">
         <v>878.22846463</v>
       </c>
-      <c r="D117">
+      <c r="E117">
         <v>867.39079782</v>
       </c>
-      <c r="E117">
+      <c r="F117">
         <v>10.83766680999997</v>
       </c>
     </row>
-    <row r="118" spans="1:5">
-      <c r="A118">
+    <row r="118" spans="1:6">
+      <c r="A118" t="s">
+        <v>122</v>
+      </c>
+      <c r="B118">
         <v>0.1</v>
       </c>
-      <c r="B118">
+      <c r="C118">
         <v>0.06</v>
       </c>
-      <c r="C118">
+      <c r="D118">
         <v>886.31593088</v>
       </c>
-      <c r="D118">
+      <c r="E118">
         <v>852.9380614</v>
       </c>
-      <c r="E118">
+      <c r="F118">
         <v>33.37786947999996</v>
       </c>
     </row>
-    <row r="119" spans="1:5">
-      <c r="A119">
+    <row r="119" spans="1:6">
+      <c r="A119" t="s">
+        <v>123</v>
+      </c>
+      <c r="B119">
         <v>0.1</v>
       </c>
-      <c r="B119">
+      <c r="C119">
         <v>0.07000000000000001</v>
       </c>
-      <c r="C119">
+      <c r="D119">
         <v>892.75772706</v>
       </c>
-      <c r="D119">
-        <v>831.00944413</v>
-      </c>
       <c r="E119">
+        <v>831.00944413</v>
+      </c>
+      <c r="F119">
         <v>61.74828292999996</v>
       </c>
     </row>
-    <row r="120" spans="1:5">
-      <c r="A120">
+    <row r="120" spans="1:6">
+      <c r="A120" t="s">
+        <v>124</v>
+      </c>
+      <c r="B120">
         <v>0.1</v>
       </c>
-      <c r="B120">
+      <c r="C120">
         <v>0.08</v>
       </c>
-      <c r="C120">
+      <c r="D120">
         <v>897.9689042</v>
       </c>
-      <c r="D120">
-        <v>831.00944413</v>
-      </c>
       <c r="E120">
+        <v>831.00944413</v>
+      </c>
+      <c r="F120">
         <v>66.95946006999998</v>
       </c>
     </row>
-    <row r="121" spans="1:5">
-      <c r="A121">
+    <row r="121" spans="1:6">
+      <c r="A121" t="s">
+        <v>125</v>
+      </c>
+      <c r="B121">
         <v>0.1</v>
       </c>
-      <c r="B121">
+      <c r="C121">
         <v>0.09</v>
       </c>
-      <c r="C121">
+      <c r="D121">
         <v>902.2200665300001</v>
       </c>
-      <c r="D121">
-        <v>831.00944413</v>
-      </c>
       <c r="E121">
+        <v>831.00944413</v>
+      </c>
+      <c r="F121">
         <v>71.21062240000003</v>
       </c>
     </row>
-    <row r="122" spans="1:5">
-      <c r="A122">
-        <v>0.1</v>
+    <row r="122" spans="1:6">
+      <c r="A122" t="s">
+        <v>126</v>
       </c>
       <c r="B122">
         <v>0.1</v>
       </c>
       <c r="C122">
+        <v>0.1</v>
+      </c>
+      <c r="D122">
         <v>905.69695384</v>
       </c>
-      <c r="D122">
-        <v>831.00944413</v>
-      </c>
       <c r="E122">
+        <v>831.00944413</v>
+      </c>
+      <c r="F122">
         <v>74.68750970999997</v>
       </c>
     </row>
